--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,6 +993,339 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104846983</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136954539</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brynjegård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518846</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7014751</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954539</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136954537</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99355</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brynjegård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>518835</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7014750</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954537</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136954536</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108456</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220107</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Klofibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crepis tectorum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Brynjegård, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>518828</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7014731</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954536</t>
         </is>
       </c>
     </row>
@@ -1001,6 +1334,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108456</v>
+        <v>108462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108462</v>
+        <v>108464</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108464</v>
+        <v>108465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108465</v>
+        <v>108471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108471</v>
+        <v>108475</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108475</v>
+        <v>108477</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108477</v>
+        <v>108479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108479</v>
+        <v>108492</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108492</v>
+        <v>108494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108494</v>
+        <v>108499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108499</v>
+        <v>108520</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108520</v>
+        <v>108521</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108521</v>
+        <v>108526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108526</v>
+        <v>108529</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108529</v>
+        <v>108535</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108535</v>
+        <v>108536</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108536</v>
+        <v>108548</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108548</v>
+        <v>108549</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108549</v>
+        <v>108552</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108552</v>
+        <v>108554</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 57478-2025 artfynd.xlsx
+++ b/artfynd/A 57478-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>136954539</v>
       </c>
       <c r="B5" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>136954537</v>
       </c>
       <c r="B6" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136954536</v>
       </c>
       <c r="B7" t="n">
-        <v>108554</v>
+        <v>108558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
